--- a/artfynd/A 20433-2026 artfynd.xlsx
+++ b/artfynd/A 20433-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134065691</v>
+        <v>134065612</v>
       </c>
       <c r="B2" t="n">
-        <v>79025</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404779</v>
+        <v>404904</v>
       </c>
       <c r="R2" t="n">
-        <v>6758789</v>
+        <v>6758723</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134065612</v>
+        <v>134065415</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404904</v>
+        <v>404608</v>
       </c>
       <c r="R3" t="n">
-        <v>6758723</v>
+        <v>6758706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134065622</v>
+        <v>134065389</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404532</v>
+        <v>404773</v>
       </c>
       <c r="R4" t="n">
-        <v>6758625</v>
+        <v>6758780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134065606</v>
+        <v>134065622</v>
       </c>
       <c r="B5" t="n">
         <v>79359</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404970</v>
+        <v>404532</v>
       </c>
       <c r="R5" t="n">
-        <v>6758887</v>
+        <v>6758625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134065373</v>
+        <v>134065687</v>
       </c>
       <c r="B6" t="n">
-        <v>79391</v>
+        <v>79025</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404660</v>
+        <v>404824</v>
       </c>
       <c r="R6" t="n">
-        <v>6758676</v>
+        <v>6758734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134065389</v>
+        <v>134065691</v>
       </c>
       <c r="B7" t="n">
-        <v>79978</v>
+        <v>79025</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404773</v>
+        <v>404779</v>
       </c>
       <c r="R7" t="n">
-        <v>6758780</v>
+        <v>6758789</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134065404</v>
+        <v>134065606</v>
       </c>
       <c r="B8" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404881</v>
+        <v>404970</v>
       </c>
       <c r="R8" t="n">
-        <v>6758713</v>
+        <v>6758887</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134065415</v>
+        <v>134065404</v>
       </c>
       <c r="B9" t="n">
         <v>79978</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404608</v>
+        <v>404881</v>
       </c>
       <c r="R9" t="n">
-        <v>6758706</v>
+        <v>6758713</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134065697</v>
+        <v>134065373</v>
       </c>
       <c r="B10" t="n">
-        <v>79025</v>
+        <v>79391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404911</v>
+        <v>404660</v>
       </c>
       <c r="R10" t="n">
-        <v>6758810</v>
+        <v>6758676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134065687</v>
+        <v>134065697</v>
       </c>
       <c r="B11" t="n">
         <v>79025</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404824</v>
+        <v>404911</v>
       </c>
       <c r="R11" t="n">
-        <v>6758734</v>
+        <v>6758810</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134065617</v>
+        <v>134065563</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404715</v>
+        <v>404771</v>
       </c>
       <c r="R14" t="n">
-        <v>6758575</v>
+        <v>6758782</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134065699</v>
+        <v>134065617</v>
       </c>
       <c r="B16" t="n">
-        <v>79025</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404849</v>
+        <v>404715</v>
       </c>
       <c r="R16" t="n">
-        <v>6758743</v>
+        <v>6758575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134065563</v>
+        <v>134065699</v>
       </c>
       <c r="B18" t="n">
-        <v>79117</v>
+        <v>79025</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404771</v>
+        <v>404849</v>
       </c>
       <c r="R18" t="n">
-        <v>6758782</v>
+        <v>6758743</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134065620</v>
+        <v>134065603</v>
       </c>
       <c r="B19" t="n">
         <v>79359</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404624</v>
+        <v>404788</v>
       </c>
       <c r="R19" t="n">
-        <v>6758605</v>
+        <v>6758782</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134065603</v>
+        <v>134065722</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>78762</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>404788</v>
+        <v>404791</v>
       </c>
       <c r="R20" t="n">
-        <v>6758782</v>
+        <v>6758773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134065722</v>
+        <v>134065620</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404791</v>
+        <v>404624</v>
       </c>
       <c r="R21" t="n">
-        <v>6758773</v>
+        <v>6758605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2922,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134065387</v>
+        <v>134065537</v>
       </c>
       <c r="B23" t="n">
-        <v>79978</v>
+        <v>79383</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404796</v>
+        <v>404567</v>
       </c>
       <c r="R23" t="n">
-        <v>6758769</v>
+        <v>6758595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,32 +3029,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134065537</v>
+        <v>134065387</v>
       </c>
       <c r="B24" t="n">
-        <v>79383</v>
+        <v>79978</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404567</v>
+        <v>404796</v>
       </c>
       <c r="R24" t="n">
-        <v>6758595</v>
+        <v>6758769</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134065407</v>
+        <v>134065390</v>
       </c>
       <c r="B25" t="n">
         <v>79978</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404727</v>
+        <v>404779</v>
       </c>
       <c r="R25" t="n">
-        <v>6758620</v>
+        <v>6758789</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3243,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134065390</v>
+        <v>134065407</v>
       </c>
       <c r="B26" t="n">
         <v>79978</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404779</v>
+        <v>404727</v>
       </c>
       <c r="R26" t="n">
-        <v>6758789</v>
+        <v>6758620</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134065381</v>
+        <v>134065703</v>
       </c>
       <c r="B27" t="n">
-        <v>79978</v>
+        <v>79025</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404845</v>
+        <v>404667</v>
       </c>
       <c r="R27" t="n">
-        <v>6758668</v>
+        <v>6758545</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,7 +3564,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134065410</v>
+        <v>134065381</v>
       </c>
       <c r="B29" t="n">
         <v>79978</v>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404594</v>
+        <v>404845</v>
       </c>
       <c r="R29" t="n">
-        <v>6758606</v>
+        <v>6758668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134065626</v>
+        <v>134065412</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404666</v>
+        <v>404548</v>
       </c>
       <c r="R30" t="n">
-        <v>6758664</v>
+        <v>6758612</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134065703</v>
+        <v>134065371</v>
       </c>
       <c r="B31" t="n">
-        <v>79025</v>
+        <v>79391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404667</v>
+        <v>404832</v>
       </c>
       <c r="R31" t="n">
-        <v>6758545</v>
+        <v>6758830</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134065412</v>
+        <v>134065609</v>
       </c>
       <c r="B32" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404548</v>
+        <v>404917</v>
       </c>
       <c r="R32" t="n">
-        <v>6758612</v>
+        <v>6758763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,7 +3992,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134065609</v>
+        <v>134065626</v>
       </c>
       <c r="B33" t="n">
         <v>79359</v>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404917</v>
+        <v>404666</v>
       </c>
       <c r="R33" t="n">
-        <v>6758763</v>
+        <v>6758664</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134065723</v>
+        <v>134065410</v>
       </c>
       <c r="B34" t="n">
-        <v>78762</v>
+        <v>79978</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404582</v>
+        <v>404594</v>
       </c>
       <c r="R34" t="n">
-        <v>6758712</v>
+        <v>6758606</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134065371</v>
+        <v>134065723</v>
       </c>
       <c r="B35" t="n">
-        <v>79391</v>
+        <v>78762</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>404832</v>
+        <v>404582</v>
       </c>
       <c r="R35" t="n">
-        <v>6758830</v>
+        <v>6758712</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,7 +4313,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134065690</v>
+        <v>134065693</v>
       </c>
       <c r="B36" t="n">
         <v>79025</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404796</v>
+        <v>404817</v>
       </c>
       <c r="R36" t="n">
-        <v>6758771</v>
+        <v>6758805</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134065692</v>
+        <v>134065399</v>
       </c>
       <c r="B37" t="n">
-        <v>79025</v>
+        <v>79978</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404800</v>
+        <v>404968</v>
       </c>
       <c r="R37" t="n">
-        <v>6758798</v>
+        <v>6758922</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,32 +4527,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134065708</v>
+        <v>134065692</v>
       </c>
       <c r="B38" t="n">
-        <v>93257</v>
+        <v>79025</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404938</v>
+        <v>404800</v>
       </c>
       <c r="R38" t="n">
-        <v>6758745</v>
+        <v>6758798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,10 +4634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134065611</v>
+        <v>134065405</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4645,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404938</v>
+        <v>404840</v>
       </c>
       <c r="R39" t="n">
-        <v>6758735</v>
+        <v>6758734</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134065405</v>
+        <v>134065611</v>
       </c>
       <c r="B40" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404840</v>
+        <v>404938</v>
       </c>
       <c r="R40" t="n">
-        <v>6758734</v>
+        <v>6758735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,10 +4848,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134065399</v>
+        <v>134065690</v>
       </c>
       <c r="B41" t="n">
-        <v>79978</v>
+        <v>79025</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4859,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4883,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404968</v>
+        <v>404796</v>
       </c>
       <c r="R41" t="n">
-        <v>6758922</v>
+        <v>6758771</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,32 +4955,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134065693</v>
+        <v>134065708</v>
       </c>
       <c r="B42" t="n">
-        <v>79025</v>
+        <v>93257</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404817</v>
+        <v>404938</v>
       </c>
       <c r="R42" t="n">
-        <v>6758805</v>
+        <v>6758745</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134065689</v>
+        <v>134065384</v>
       </c>
       <c r="B44" t="n">
-        <v>79025</v>
+        <v>79978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5180,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404823</v>
+        <v>404810</v>
       </c>
       <c r="R44" t="n">
-        <v>6758753</v>
+        <v>6758738</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134065698</v>
+        <v>134065388</v>
       </c>
       <c r="B45" t="n">
-        <v>79025</v>
+        <v>79978</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404915</v>
+        <v>404787</v>
       </c>
       <c r="R45" t="n">
-        <v>6758802</v>
+        <v>6758776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,7 +5383,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134065388</v>
+        <v>134065403</v>
       </c>
       <c r="B46" t="n">
         <v>79978</v>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404787</v>
+        <v>404906</v>
       </c>
       <c r="R46" t="n">
-        <v>6758776</v>
+        <v>6758705</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134065403</v>
+        <v>134065689</v>
       </c>
       <c r="B47" t="n">
-        <v>79978</v>
+        <v>79025</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404906</v>
+        <v>404823</v>
       </c>
       <c r="R47" t="n">
-        <v>6758705</v>
+        <v>6758753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134065384</v>
+        <v>134065698</v>
       </c>
       <c r="B48" t="n">
-        <v>79978</v>
+        <v>79025</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404810</v>
+        <v>404915</v>
       </c>
       <c r="R48" t="n">
-        <v>6758738</v>
+        <v>6758802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134065372</v>
+        <v>134065395</v>
       </c>
       <c r="B49" t="n">
-        <v>79391</v>
+        <v>79978</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404659</v>
+        <v>404888</v>
       </c>
       <c r="R49" t="n">
-        <v>6758699</v>
+        <v>6758894</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,32 +5811,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134065535</v>
+        <v>134065372</v>
       </c>
       <c r="B50" t="n">
-        <v>79383</v>
+        <v>79391</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404829</v>
+        <v>404659</v>
       </c>
       <c r="R50" t="n">
-        <v>6758826</v>
+        <v>6758699</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,32 +5918,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134065561</v>
+        <v>134065535</v>
       </c>
       <c r="B51" t="n">
-        <v>79117</v>
+        <v>79383</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404847</v>
+        <v>404829</v>
       </c>
       <c r="R51" t="n">
-        <v>6758670</v>
+        <v>6758826</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134065395</v>
+        <v>134065561</v>
       </c>
       <c r="B52" t="n">
-        <v>79978</v>
+        <v>79117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404888</v>
+        <v>404847</v>
       </c>
       <c r="R52" t="n">
-        <v>6758894</v>
+        <v>6758670</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134065624</v>
+        <v>134065721</v>
       </c>
       <c r="B53" t="n">
-        <v>79359</v>
+        <v>78363</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404660</v>
+        <v>404791</v>
       </c>
       <c r="R53" t="n">
-        <v>6758694</v>
+        <v>6758773</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134065496</v>
+        <v>134065385</v>
       </c>
       <c r="B54" t="n">
-        <v>57972</v>
+        <v>79978</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,39 +6250,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404969</v>
+        <v>404814</v>
       </c>
       <c r="R54" t="n">
-        <v>6758939</v>
+        <v>6758745</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6314,7 +6309,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6324,7 +6319,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6351,10 +6346,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134065721</v>
+        <v>134065496</v>
       </c>
       <c r="B55" t="n">
-        <v>78363</v>
+        <v>57972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6362,34 +6357,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6487</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404791</v>
+        <v>404969</v>
       </c>
       <c r="R55" t="n">
-        <v>6758773</v>
+        <v>6758939</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6565,10 +6565,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134065385</v>
+        <v>134065624</v>
       </c>
       <c r="B57" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404814</v>
+        <v>404660</v>
       </c>
       <c r="R57" t="n">
-        <v>6758745</v>
+        <v>6758694</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,10 +6672,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134065538</v>
+        <v>134065705</v>
       </c>
       <c r="B58" t="n">
-        <v>79383</v>
+        <v>93257</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6683,21 +6683,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404572</v>
+        <v>404776</v>
       </c>
       <c r="R58" t="n">
-        <v>6758703</v>
+        <v>6758787</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6779,32 +6779,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134065604</v>
+        <v>134065538</v>
       </c>
       <c r="B59" t="n">
-        <v>79359</v>
+        <v>79383</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404978</v>
+        <v>404572</v>
       </c>
       <c r="R59" t="n">
-        <v>6758991</v>
+        <v>6758703</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,32 +6886,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134065705</v>
+        <v>134065629</v>
       </c>
       <c r="B60" t="n">
-        <v>93257</v>
+        <v>79359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404776</v>
+        <v>404677</v>
       </c>
       <c r="R60" t="n">
-        <v>6758787</v>
+        <v>6758528</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,7 +6993,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134065629</v>
+        <v>134065604</v>
       </c>
       <c r="B61" t="n">
         <v>79359</v>
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404677</v>
+        <v>404978</v>
       </c>
       <c r="R61" t="n">
-        <v>6758528</v>
+        <v>6758991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7100,7 +7100,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134065619</v>
+        <v>134065607</v>
       </c>
       <c r="B62" t="n">
         <v>79359</v>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404697</v>
+        <v>404936</v>
       </c>
       <c r="R62" t="n">
-        <v>6758567</v>
+        <v>6758864</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7207,10 +7207,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134065623</v>
+        <v>134065701</v>
       </c>
       <c r="B63" t="n">
-        <v>79359</v>
+        <v>79025</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7218,21 +7218,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404582</v>
+        <v>404593</v>
       </c>
       <c r="R63" t="n">
-        <v>6758712</v>
+        <v>6758609</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7314,10 +7314,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134065701</v>
+        <v>134065619</v>
       </c>
       <c r="B64" t="n">
-        <v>79025</v>
+        <v>79359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,21 +7325,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404593</v>
+        <v>404697</v>
       </c>
       <c r="R64" t="n">
-        <v>6758609</v>
+        <v>6758567</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7421,7 +7421,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134065607</v>
+        <v>134065623</v>
       </c>
       <c r="B65" t="n">
         <v>79359</v>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404936</v>
+        <v>404582</v>
       </c>
       <c r="R65" t="n">
-        <v>6758864</v>
+        <v>6758712</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7635,7 +7635,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134065402</v>
+        <v>134065411</v>
       </c>
       <c r="B67" t="n">
         <v>79978</v>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404938</v>
+        <v>404590</v>
       </c>
       <c r="R67" t="n">
-        <v>6758742</v>
+        <v>6758604</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7742,7 +7742,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134065411</v>
+        <v>134065396</v>
       </c>
       <c r="B68" t="n">
         <v>79978</v>
@@ -7777,10 +7777,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404590</v>
+        <v>404893</v>
       </c>
       <c r="R68" t="n">
-        <v>6758604</v>
+        <v>6758895</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7849,7 +7849,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134065396</v>
+        <v>134065402</v>
       </c>
       <c r="B69" t="n">
         <v>79978</v>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404893</v>
+        <v>404938</v>
       </c>
       <c r="R69" t="n">
-        <v>6758895</v>
+        <v>6758742</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8063,7 +8063,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134065417</v>
+        <v>134065400</v>
       </c>
       <c r="B71" t="n">
         <v>79978</v>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404662</v>
+        <v>404899</v>
       </c>
       <c r="R71" t="n">
-        <v>6758649</v>
+        <v>6758863</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8170,10 +8170,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134065627</v>
+        <v>134065374</v>
       </c>
       <c r="B72" t="n">
-        <v>79359</v>
+        <v>79391</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8181,21 +8181,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404660</v>
+        <v>404663</v>
       </c>
       <c r="R72" t="n">
-        <v>6758643</v>
+        <v>6758651</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134065374</v>
+        <v>134065615</v>
       </c>
       <c r="B73" t="n">
-        <v>79391</v>
+        <v>79359</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8288,21 +8288,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8312,10 +8312,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404663</v>
+        <v>404723</v>
       </c>
       <c r="R73" t="n">
-        <v>6758651</v>
+        <v>6758594</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8384,10 +8384,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134065615</v>
+        <v>134065417</v>
       </c>
       <c r="B74" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8395,21 +8395,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404723</v>
+        <v>404662</v>
       </c>
       <c r="R74" t="n">
-        <v>6758594</v>
+        <v>6758649</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8491,10 +8491,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134065400</v>
+        <v>134065627</v>
       </c>
       <c r="B75" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8502,21 +8502,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404899</v>
+        <v>404660</v>
       </c>
       <c r="R75" t="n">
-        <v>6758863</v>
+        <v>6758643</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8598,10 +8598,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134065534</v>
+        <v>134065614</v>
       </c>
       <c r="B76" t="n">
-        <v>93249</v>
+        <v>79359</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8609,21 +8609,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404836</v>
+        <v>404734</v>
       </c>
       <c r="R76" t="n">
-        <v>6758673</v>
+        <v>6758630</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8678,19 +8678,14 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -8710,10 +8705,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134065562</v>
+        <v>134065688</v>
       </c>
       <c r="B77" t="n">
-        <v>79117</v>
+        <v>79025</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8721,21 +8716,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8745,10 +8740,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404815</v>
+        <v>404803</v>
       </c>
       <c r="R77" t="n">
-        <v>6758748</v>
+        <v>6758731</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8780,7 +8775,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8790,7 +8785,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8817,10 +8812,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134065688</v>
+        <v>134065562</v>
       </c>
       <c r="B78" t="n">
-        <v>79025</v>
+        <v>79117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8828,21 +8823,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8852,10 +8847,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404803</v>
+        <v>404815</v>
       </c>
       <c r="R78" t="n">
-        <v>6758731</v>
+        <v>6758748</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8887,7 +8882,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8897,7 +8892,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8924,10 +8919,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134065614</v>
+        <v>134065534</v>
       </c>
       <c r="B79" t="n">
-        <v>79359</v>
+        <v>93249</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8935,21 +8930,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8959,10 +8954,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404734</v>
+        <v>404836</v>
       </c>
       <c r="R79" t="n">
-        <v>6758630</v>
+        <v>6758673</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8994,7 +8989,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9004,14 +8999,19 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -9031,7 +9031,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134065406</v>
+        <v>134065392</v>
       </c>
       <c r="B80" t="n">
         <v>79978</v>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>404736</v>
+        <v>404778</v>
       </c>
       <c r="R80" t="n">
-        <v>6758627</v>
+        <v>6758818</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9138,10 +9138,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134065625</v>
+        <v>134065406</v>
       </c>
       <c r="B81" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9149,21 +9149,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>404658</v>
+        <v>404736</v>
       </c>
       <c r="R81" t="n">
-        <v>6758686</v>
+        <v>6758627</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9245,10 +9245,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134065392</v>
+        <v>134065593</v>
       </c>
       <c r="B82" t="n">
-        <v>79978</v>
+        <v>79116</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>404778</v>
+        <v>404673</v>
       </c>
       <c r="R82" t="n">
-        <v>6758818</v>
+        <v>6758546</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9352,10 +9352,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134065593</v>
+        <v>134065625</v>
       </c>
       <c r="B83" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>404673</v>
+        <v>404658</v>
       </c>
       <c r="R83" t="n">
-        <v>6758546</v>
+        <v>6758686</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9459,32 +9459,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134065383</v>
+        <v>134065536</v>
       </c>
       <c r="B84" t="n">
-        <v>79978</v>
+        <v>79383</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>404810</v>
+        <v>404959</v>
       </c>
       <c r="R84" t="n">
-        <v>6758727</v>
+        <v>6758961</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9566,10 +9566,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134065565</v>
+        <v>134065621</v>
       </c>
       <c r="B85" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9577,21 +9577,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9601,10 +9601,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>404911</v>
+        <v>404593</v>
       </c>
       <c r="R85" t="n">
-        <v>6758810</v>
+        <v>6758609</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9780,32 +9780,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134065536</v>
+        <v>134065383</v>
       </c>
       <c r="B87" t="n">
-        <v>79383</v>
+        <v>79978</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>404959</v>
+        <v>404810</v>
       </c>
       <c r="R87" t="n">
-        <v>6758961</v>
+        <v>6758727</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9887,10 +9887,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134065621</v>
+        <v>134065565</v>
       </c>
       <c r="B88" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9898,21 +9898,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>404593</v>
+        <v>404911</v>
       </c>
       <c r="R88" t="n">
-        <v>6758609</v>
+        <v>6758810</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9994,10 +9994,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134065616</v>
+        <v>134065418</v>
       </c>
       <c r="B89" t="n">
-        <v>79359</v>
+        <v>79949</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10005,21 +10005,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>404717</v>
+        <v>404822</v>
       </c>
       <c r="R89" t="n">
-        <v>6758579</v>
+        <v>6758751</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10208,10 +10208,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134065610</v>
+        <v>134065393</v>
       </c>
       <c r="B91" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10219,21 +10219,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>404943</v>
+        <v>404824</v>
       </c>
       <c r="R91" t="n">
-        <v>6758755</v>
+        <v>6758793</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10315,10 +10315,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134065393</v>
+        <v>134065610</v>
       </c>
       <c r="B92" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10326,21 +10326,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>404824</v>
+        <v>404943</v>
       </c>
       <c r="R92" t="n">
-        <v>6758793</v>
+        <v>6758755</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134065418</v>
+        <v>134065616</v>
       </c>
       <c r="B93" t="n">
-        <v>79949</v>
+        <v>79359</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>404822</v>
+        <v>404717</v>
       </c>
       <c r="R93" t="n">
-        <v>6758751</v>
+        <v>6758579</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10529,10 +10529,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134065591</v>
+        <v>134065541</v>
       </c>
       <c r="B94" t="n">
-        <v>79116</v>
+        <v>92013</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10540,21 +10540,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>404978</v>
+        <v>404532</v>
       </c>
       <c r="R94" t="n">
-        <v>6758880</v>
+        <v>6758663</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134065541</v>
+        <v>134065413</v>
       </c>
       <c r="B96" t="n">
-        <v>92013</v>
+        <v>79978</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10778,10 +10778,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>404532</v>
+        <v>404527</v>
       </c>
       <c r="R96" t="n">
-        <v>6758663</v>
+        <v>6758680</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10850,10 +10850,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134065413</v>
+        <v>134065591</v>
       </c>
       <c r="B97" t="n">
-        <v>79978</v>
+        <v>79116</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10861,21 +10861,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>404527</v>
+        <v>404978</v>
       </c>
       <c r="R97" t="n">
-        <v>6758680</v>
+        <v>6758880</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10957,10 +10957,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134065566</v>
+        <v>134065592</v>
       </c>
       <c r="B98" t="n">
-        <v>79117</v>
+        <v>79116</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10968,21 +10968,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10992,10 +10992,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>404898</v>
+        <v>404894</v>
       </c>
       <c r="R98" t="n">
-        <v>6758708</v>
+        <v>6758696</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134065618</v>
+        <v>134065397</v>
       </c>
       <c r="B99" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11075,21 +11075,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11099,10 +11099,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>404705</v>
+        <v>404910</v>
       </c>
       <c r="R99" t="n">
-        <v>6758564</v>
+        <v>6758935</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11171,7 +11171,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134065397</v>
+        <v>134065398</v>
       </c>
       <c r="B100" t="n">
         <v>79978</v>
@@ -11206,10 +11206,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>404910</v>
+        <v>404973</v>
       </c>
       <c r="R100" t="n">
-        <v>6758935</v>
+        <v>6759009</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11278,10 +11278,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134065394</v>
+        <v>134065566</v>
       </c>
       <c r="B101" t="n">
-        <v>79978</v>
+        <v>79117</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11289,21 +11289,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>404814</v>
+        <v>404898</v>
       </c>
       <c r="R101" t="n">
-        <v>6758813</v>
+        <v>6758708</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11385,10 +11385,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134065592</v>
+        <v>134065618</v>
       </c>
       <c r="B102" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11396,21 +11396,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11420,10 +11420,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>404894</v>
+        <v>404705</v>
       </c>
       <c r="R102" t="n">
-        <v>6758696</v>
+        <v>6758564</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11492,7 +11492,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134065398</v>
+        <v>134065394</v>
       </c>
       <c r="B103" t="n">
         <v>79978</v>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>404973</v>
+        <v>404814</v>
       </c>
       <c r="R103" t="n">
-        <v>6759009</v>
+        <v>6758813</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11706,10 +11706,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134065391</v>
+        <v>134065608</v>
       </c>
       <c r="B105" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11717,21 +11717,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11741,10 +11741,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>404801</v>
+        <v>404872</v>
       </c>
       <c r="R105" t="n">
-        <v>6758801</v>
+        <v>6758869</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11920,32 +11920,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134065597</v>
+        <v>134065421</v>
       </c>
       <c r="B107" t="n">
-        <v>92139</v>
+        <v>79949</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11955,10 +11955,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>404908</v>
+        <v>404659</v>
       </c>
       <c r="R107" t="n">
-        <v>6758934</v>
+        <v>6758702</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12027,10 +12027,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134065421</v>
+        <v>134065391</v>
       </c>
       <c r="B108" t="n">
-        <v>79949</v>
+        <v>79978</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12038,21 +12038,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12062,10 +12062,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>404659</v>
+        <v>404801</v>
       </c>
       <c r="R108" t="n">
-        <v>6758702</v>
+        <v>6758801</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12241,32 +12241,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134065608</v>
+        <v>134065597</v>
       </c>
       <c r="B110" t="n">
-        <v>79359</v>
+        <v>92139</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>404872</v>
+        <v>404908</v>
       </c>
       <c r="R110" t="n">
-        <v>6758869</v>
+        <v>6758934</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 20433-2026 artfynd.xlsx
+++ b/artfynd/A 20433-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134065612</v>
+        <v>134065373</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404904</v>
+        <v>404660</v>
       </c>
       <c r="R2" t="n">
-        <v>6758723</v>
+        <v>6758676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134065415</v>
+        <v>134065389</v>
       </c>
       <c r="B3" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404608</v>
+        <v>404773</v>
       </c>
       <c r="R3" t="n">
-        <v>6758706</v>
+        <v>6758780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134065389</v>
+        <v>134065687</v>
       </c>
       <c r="B4" t="n">
-        <v>79978</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404773</v>
+        <v>404824</v>
       </c>
       <c r="R4" t="n">
-        <v>6758780</v>
+        <v>6758734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134065622</v>
+        <v>134065415</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404532</v>
+        <v>404608</v>
       </c>
       <c r="R5" t="n">
-        <v>6758625</v>
+        <v>6758706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134065687</v>
+        <v>134065622</v>
       </c>
       <c r="B6" t="n">
-        <v>79025</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404824</v>
+        <v>404532</v>
       </c>
       <c r="R6" t="n">
-        <v>6758734</v>
+        <v>6758625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134065691</v>
+        <v>134065612</v>
       </c>
       <c r="B7" t="n">
-        <v>79025</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404779</v>
+        <v>404904</v>
       </c>
       <c r="R7" t="n">
-        <v>6758789</v>
+        <v>6758723</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>134065606</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134065404</v>
+        <v>134065691</v>
       </c>
       <c r="B9" t="n">
-        <v>79978</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404881</v>
+        <v>404779</v>
       </c>
       <c r="R9" t="n">
-        <v>6758713</v>
+        <v>6758789</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134065373</v>
+        <v>134065404</v>
       </c>
       <c r="B10" t="n">
-        <v>79391</v>
+        <v>79985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404660</v>
+        <v>404881</v>
       </c>
       <c r="R10" t="n">
-        <v>6758676</v>
+        <v>6758713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
         <v>134065697</v>
       </c>
       <c r="B11" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134065706</v>
+        <v>134065382</v>
       </c>
       <c r="B12" t="n">
-        <v>93257</v>
+        <v>79985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404815</v>
+        <v>404824</v>
       </c>
       <c r="R12" t="n">
-        <v>6758798</v>
+        <v>6758734</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134065382</v>
+        <v>134065617</v>
       </c>
       <c r="B13" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404824</v>
+        <v>404715</v>
       </c>
       <c r="R13" t="n">
-        <v>6758734</v>
+        <v>6758575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134065563</v>
+        <v>134065386</v>
       </c>
       <c r="B14" t="n">
-        <v>79117</v>
+        <v>79985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404771</v>
+        <v>404811</v>
       </c>
       <c r="R14" t="n">
-        <v>6758782</v>
+        <v>6758761</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134065386</v>
+        <v>134065699</v>
       </c>
       <c r="B15" t="n">
-        <v>79978</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404811</v>
+        <v>404849</v>
       </c>
       <c r="R15" t="n">
-        <v>6758761</v>
+        <v>6758743</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134065617</v>
+        <v>134065416</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404715</v>
+        <v>404659</v>
       </c>
       <c r="R16" t="n">
-        <v>6758575</v>
+        <v>6758702</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134065416</v>
+        <v>134065563</v>
       </c>
       <c r="B17" t="n">
-        <v>79978</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404659</v>
+        <v>404771</v>
       </c>
       <c r="R17" t="n">
-        <v>6758702</v>
+        <v>6758782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134065699</v>
+        <v>134065706</v>
       </c>
       <c r="B18" t="n">
-        <v>79025</v>
+        <v>93264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404849</v>
+        <v>404815</v>
       </c>
       <c r="R18" t="n">
-        <v>6758743</v>
+        <v>6758798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134065603</v>
+        <v>134065620</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404788</v>
+        <v>404624</v>
       </c>
       <c r="R19" t="n">
-        <v>6758782</v>
+        <v>6758605</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134065722</v>
+        <v>134065387</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>79985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>404791</v>
+        <v>404796</v>
       </c>
       <c r="R20" t="n">
-        <v>6758773</v>
+        <v>6758769</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134065620</v>
+        <v>134065603</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404624</v>
+        <v>404788</v>
       </c>
       <c r="R21" t="n">
-        <v>6758605</v>
+        <v>6758782</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,7 +2818,7 @@
         <v>134065567</v>
       </c>
       <c r="B22" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>134065537</v>
       </c>
       <c r="B23" t="n">
-        <v>79383</v>
+        <v>79390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134065387</v>
+        <v>134065722</v>
       </c>
       <c r="B24" t="n">
-        <v>79978</v>
+        <v>78769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404796</v>
+        <v>404791</v>
       </c>
       <c r="R24" t="n">
-        <v>6758769</v>
+        <v>6758773</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3139,7 +3139,7 @@
         <v>134065390</v>
       </c>
       <c r="B25" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>134065407</v>
       </c>
       <c r="B26" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134065703</v>
+        <v>134065381</v>
       </c>
       <c r="B27" t="n">
-        <v>79025</v>
+        <v>79985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404667</v>
+        <v>404845</v>
       </c>
       <c r="R27" t="n">
-        <v>6758545</v>
+        <v>6758668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3457,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134065401</v>
+        <v>134065703</v>
       </c>
       <c r="B28" t="n">
-        <v>79978</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404911</v>
+        <v>404667</v>
       </c>
       <c r="R28" t="n">
-        <v>6758810</v>
+        <v>6758545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134065381</v>
+        <v>134065723</v>
       </c>
       <c r="B29" t="n">
-        <v>79978</v>
+        <v>78769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404845</v>
+        <v>404582</v>
       </c>
       <c r="R29" t="n">
-        <v>6758668</v>
+        <v>6758712</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3674,7 +3674,7 @@
         <v>134065412</v>
       </c>
       <c r="B30" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3778,10 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134065371</v>
+        <v>134065401</v>
       </c>
       <c r="B31" t="n">
-        <v>79391</v>
+        <v>79985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404832</v>
+        <v>404911</v>
       </c>
       <c r="R31" t="n">
-        <v>6758830</v>
+        <v>6758810</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,10 +3885,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134065609</v>
+        <v>134065371</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>79398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404917</v>
+        <v>404832</v>
       </c>
       <c r="R32" t="n">
-        <v>6758763</v>
+        <v>6758830</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,10 +3992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134065626</v>
+        <v>134065609</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404666</v>
+        <v>404917</v>
       </c>
       <c r="R33" t="n">
-        <v>6758664</v>
+        <v>6758763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,10 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134065410</v>
+        <v>134065626</v>
       </c>
       <c r="B34" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404594</v>
+        <v>404666</v>
       </c>
       <c r="R34" t="n">
-        <v>6758606</v>
+        <v>6758664</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134065723</v>
+        <v>134065410</v>
       </c>
       <c r="B35" t="n">
-        <v>78762</v>
+        <v>79985</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4217,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>404582</v>
+        <v>404594</v>
       </c>
       <c r="R35" t="n">
-        <v>6758712</v>
+        <v>6758606</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,32 +4313,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134065693</v>
+        <v>134065708</v>
       </c>
       <c r="B36" t="n">
-        <v>79025</v>
+        <v>93264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>404817</v>
+        <v>404938</v>
       </c>
       <c r="R36" t="n">
-        <v>6758805</v>
+        <v>6758745</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134065399</v>
+        <v>134065692</v>
       </c>
       <c r="B37" t="n">
-        <v>79978</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4431,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404968</v>
+        <v>404800</v>
       </c>
       <c r="R37" t="n">
-        <v>6758922</v>
+        <v>6758798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,10 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134065692</v>
+        <v>134065611</v>
       </c>
       <c r="B38" t="n">
-        <v>79025</v>
+        <v>79366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4562,10 +4562,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404800</v>
+        <v>404938</v>
       </c>
       <c r="R38" t="n">
-        <v>6758798</v>
+        <v>6758735</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4637,7 +4637,7 @@
         <v>134065405</v>
       </c>
       <c r="B39" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4741,10 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134065611</v>
+        <v>134065399</v>
       </c>
       <c r="B40" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404938</v>
+        <v>404968</v>
       </c>
       <c r="R40" t="n">
-        <v>6758735</v>
+        <v>6758922</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4851,7 +4851,7 @@
         <v>134065690</v>
       </c>
       <c r="B41" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4955,32 +4955,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134065708</v>
+        <v>134065693</v>
       </c>
       <c r="B42" t="n">
-        <v>93257</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404938</v>
+        <v>404817</v>
       </c>
       <c r="R42" t="n">
-        <v>6758745</v>
+        <v>6758805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,10 +5062,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134065564</v>
+        <v>134065698</v>
       </c>
       <c r="B43" t="n">
-        <v>79117</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404972</v>
+        <v>404915</v>
       </c>
       <c r="R43" t="n">
-        <v>6758882</v>
+        <v>6758802</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5169,10 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134065384</v>
+        <v>134065403</v>
       </c>
       <c r="B44" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5204,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404810</v>
+        <v>404906</v>
       </c>
       <c r="R44" t="n">
-        <v>6758738</v>
+        <v>6758705</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,10 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134065388</v>
+        <v>134065564</v>
       </c>
       <c r="B45" t="n">
-        <v>79978</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404787</v>
+        <v>404972</v>
       </c>
       <c r="R45" t="n">
-        <v>6758776</v>
+        <v>6758882</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,10 +5383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134065403</v>
+        <v>134065689</v>
       </c>
       <c r="B46" t="n">
-        <v>79978</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,21 +5394,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404906</v>
+        <v>404823</v>
       </c>
       <c r="R46" t="n">
-        <v>6758705</v>
+        <v>6758753</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,10 +5490,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134065689</v>
+        <v>134065384</v>
       </c>
       <c r="B47" t="n">
-        <v>79025</v>
+        <v>79985</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404823</v>
+        <v>404810</v>
       </c>
       <c r="R47" t="n">
-        <v>6758753</v>
+        <v>6758738</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,10 +5597,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134065698</v>
+        <v>134065388</v>
       </c>
       <c r="B48" t="n">
-        <v>79025</v>
+        <v>79985</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5608,21 +5608,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404915</v>
+        <v>404787</v>
       </c>
       <c r="R48" t="n">
-        <v>6758802</v>
+        <v>6758776</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134065395</v>
+        <v>134065372</v>
       </c>
       <c r="B49" t="n">
-        <v>79978</v>
+        <v>79398</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,21 +5715,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5739,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404888</v>
+        <v>404659</v>
       </c>
       <c r="R49" t="n">
-        <v>6758894</v>
+        <v>6758699</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,32 +5811,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134065372</v>
+        <v>134065535</v>
       </c>
       <c r="B50" t="n">
-        <v>79391</v>
+        <v>79390</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404659</v>
+        <v>404829</v>
       </c>
       <c r="R50" t="n">
-        <v>6758699</v>
+        <v>6758826</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,32 +5918,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134065535</v>
+        <v>134065561</v>
       </c>
       <c r="B51" t="n">
-        <v>79383</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404829</v>
+        <v>404847</v>
       </c>
       <c r="R51" t="n">
-        <v>6758826</v>
+        <v>6758670</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,10 +6025,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134065561</v>
+        <v>134065395</v>
       </c>
       <c r="B52" t="n">
-        <v>79117</v>
+        <v>79985</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404847</v>
+        <v>404888</v>
       </c>
       <c r="R52" t="n">
-        <v>6758670</v>
+        <v>6758894</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,10 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134065721</v>
+        <v>134065624</v>
       </c>
       <c r="B53" t="n">
-        <v>78363</v>
+        <v>79366</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404791</v>
+        <v>404660</v>
       </c>
       <c r="R53" t="n">
-        <v>6758773</v>
+        <v>6758694</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134065385</v>
+        <v>134065496</v>
       </c>
       <c r="B54" t="n">
-        <v>79978</v>
+        <v>57972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6250,34 +6250,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404814</v>
+        <v>404969</v>
       </c>
       <c r="R54" t="n">
-        <v>6758745</v>
+        <v>6758939</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6309,7 +6314,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6319,7 +6324,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6346,10 +6351,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134065496</v>
+        <v>134065721</v>
       </c>
       <c r="B55" t="n">
-        <v>57972</v>
+        <v>78370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6357,39 +6362,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404969</v>
+        <v>404791</v>
       </c>
       <c r="R55" t="n">
-        <v>6758939</v>
+        <v>6758773</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6461,7 +6461,7 @@
         <v>134065419</v>
       </c>
       <c r="B56" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134065624</v>
+        <v>134065385</v>
       </c>
       <c r="B57" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404660</v>
+        <v>404814</v>
       </c>
       <c r="R57" t="n">
-        <v>6758694</v>
+        <v>6758745</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6675,7 +6675,7 @@
         <v>134065705</v>
       </c>
       <c r="B58" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6779,32 +6779,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134065538</v>
+        <v>134065629</v>
       </c>
       <c r="B59" t="n">
-        <v>79383</v>
+        <v>79366</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404572</v>
+        <v>404677</v>
       </c>
       <c r="R59" t="n">
-        <v>6758703</v>
+        <v>6758528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,32 +6886,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134065629</v>
+        <v>134065538</v>
       </c>
       <c r="B60" t="n">
-        <v>79359</v>
+        <v>79390</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404677</v>
+        <v>404572</v>
       </c>
       <c r="R60" t="n">
-        <v>6758528</v>
+        <v>6758703</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6996,7 +6996,7 @@
         <v>134065604</v>
       </c>
       <c r="B61" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7100,10 +7100,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134065607</v>
+        <v>134065701</v>
       </c>
       <c r="B62" t="n">
-        <v>79359</v>
+        <v>79032</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7111,21 +7111,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404936</v>
+        <v>404593</v>
       </c>
       <c r="R62" t="n">
-        <v>6758864</v>
+        <v>6758609</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7207,10 +7207,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134065701</v>
+        <v>134065623</v>
       </c>
       <c r="B63" t="n">
-        <v>79025</v>
+        <v>79366</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7218,21 +7218,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7242,10 +7242,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404593</v>
+        <v>404582</v>
       </c>
       <c r="R63" t="n">
-        <v>6758609</v>
+        <v>6758712</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7314,10 +7314,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134065619</v>
+        <v>134065607</v>
       </c>
       <c r="B64" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404697</v>
+        <v>404936</v>
       </c>
       <c r="R64" t="n">
-        <v>6758567</v>
+        <v>6758864</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7421,10 +7421,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134065623</v>
+        <v>134065605</v>
       </c>
       <c r="B65" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404582</v>
+        <v>404960</v>
       </c>
       <c r="R65" t="n">
-        <v>6758712</v>
+        <v>6758909</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7528,10 +7528,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134065605</v>
+        <v>134065619</v>
       </c>
       <c r="B66" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404960</v>
+        <v>404697</v>
       </c>
       <c r="R66" t="n">
-        <v>6758909</v>
+        <v>6758567</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7635,10 +7635,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134065411</v>
+        <v>134065402</v>
       </c>
       <c r="B67" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404590</v>
+        <v>404938</v>
       </c>
       <c r="R67" t="n">
-        <v>6758604</v>
+        <v>6758742</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7745,7 +7745,7 @@
         <v>134065396</v>
       </c>
       <c r="B68" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7849,10 +7849,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134065402</v>
+        <v>134065411</v>
       </c>
       <c r="B69" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404938</v>
+        <v>404590</v>
       </c>
       <c r="R69" t="n">
-        <v>6758742</v>
+        <v>6758604</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7959,7 +7959,7 @@
         <v>134065695</v>
       </c>
       <c r="B70" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8063,10 +8063,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134065400</v>
+        <v>134065417</v>
       </c>
       <c r="B71" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404899</v>
+        <v>404662</v>
       </c>
       <c r="R71" t="n">
-        <v>6758863</v>
+        <v>6758649</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8170,10 +8170,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134065374</v>
+        <v>134065627</v>
       </c>
       <c r="B72" t="n">
-        <v>79391</v>
+        <v>79366</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8181,21 +8181,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8205,10 +8205,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404663</v>
+        <v>404660</v>
       </c>
       <c r="R72" t="n">
-        <v>6758651</v>
+        <v>6758643</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8277,10 +8277,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134065615</v>
+        <v>134065374</v>
       </c>
       <c r="B73" t="n">
-        <v>79359</v>
+        <v>79398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8288,21 +8288,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8312,10 +8312,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404723</v>
+        <v>404663</v>
       </c>
       <c r="R73" t="n">
-        <v>6758594</v>
+        <v>6758651</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8384,10 +8384,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134065417</v>
+        <v>134065615</v>
       </c>
       <c r="B74" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8395,21 +8395,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404662</v>
+        <v>404723</v>
       </c>
       <c r="R74" t="n">
-        <v>6758649</v>
+        <v>6758594</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8491,10 +8491,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134065627</v>
+        <v>134065400</v>
       </c>
       <c r="B75" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8502,21 +8502,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404660</v>
+        <v>404899</v>
       </c>
       <c r="R75" t="n">
-        <v>6758643</v>
+        <v>6758863</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8598,10 +8598,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134065614</v>
+        <v>134065562</v>
       </c>
       <c r="B76" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8609,21 +8609,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404734</v>
+        <v>404815</v>
       </c>
       <c r="R76" t="n">
-        <v>6758630</v>
+        <v>6758748</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,10 +8705,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134065688</v>
+        <v>134065614</v>
       </c>
       <c r="B77" t="n">
-        <v>79025</v>
+        <v>79366</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8716,21 +8716,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404803</v>
+        <v>404734</v>
       </c>
       <c r="R77" t="n">
-        <v>6758731</v>
+        <v>6758630</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,10 +8812,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134065562</v>
+        <v>134065534</v>
       </c>
       <c r="B78" t="n">
-        <v>79117</v>
+        <v>93256</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8823,21 +8823,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404815</v>
+        <v>404836</v>
       </c>
       <c r="R78" t="n">
-        <v>6758748</v>
+        <v>6758673</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8892,14 +8892,19 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -8919,10 +8924,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134065534</v>
+        <v>134065688</v>
       </c>
       <c r="B79" t="n">
-        <v>93249</v>
+        <v>79032</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8930,21 +8935,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8954,10 +8959,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404836</v>
+        <v>404803</v>
       </c>
       <c r="R79" t="n">
-        <v>6758673</v>
+        <v>6758731</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8989,7 +8994,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8999,19 +9004,14 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -9031,10 +9031,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134065392</v>
+        <v>134065593</v>
       </c>
       <c r="B80" t="n">
-        <v>79978</v>
+        <v>79123</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9042,21 +9042,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9066,10 +9066,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>404778</v>
+        <v>404673</v>
       </c>
       <c r="R80" t="n">
-        <v>6758818</v>
+        <v>6758546</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9138,10 +9138,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134065406</v>
+        <v>134065625</v>
       </c>
       <c r="B81" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9149,21 +9149,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9173,10 +9173,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>404736</v>
+        <v>404658</v>
       </c>
       <c r="R81" t="n">
-        <v>6758627</v>
+        <v>6758686</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9245,10 +9245,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134065593</v>
+        <v>134065392</v>
       </c>
       <c r="B82" t="n">
-        <v>79116</v>
+        <v>79985</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9256,21 +9256,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>404673</v>
+        <v>404778</v>
       </c>
       <c r="R82" t="n">
-        <v>6758546</v>
+        <v>6758818</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9352,10 +9352,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134065625</v>
+        <v>134065406</v>
       </c>
       <c r="B83" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9363,21 +9363,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>404658</v>
+        <v>404736</v>
       </c>
       <c r="R83" t="n">
-        <v>6758686</v>
+        <v>6758627</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9459,32 +9459,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134065536</v>
+        <v>134065383</v>
       </c>
       <c r="B84" t="n">
-        <v>79383</v>
+        <v>79985</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9494,10 +9494,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>404959</v>
+        <v>404810</v>
       </c>
       <c r="R84" t="n">
-        <v>6758961</v>
+        <v>6758727</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9566,10 +9566,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134065621</v>
+        <v>134065565</v>
       </c>
       <c r="B85" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9577,21 +9577,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9601,10 +9601,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>404593</v>
+        <v>404911</v>
       </c>
       <c r="R85" t="n">
-        <v>6758609</v>
+        <v>6758810</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9673,32 +9673,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134065613</v>
+        <v>134065536</v>
       </c>
       <c r="B86" t="n">
-        <v>79359</v>
+        <v>79390</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>404868</v>
+        <v>404959</v>
       </c>
       <c r="R86" t="n">
-        <v>6758717</v>
+        <v>6758961</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9780,10 +9780,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134065383</v>
+        <v>134065621</v>
       </c>
       <c r="B87" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9791,21 +9791,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>404810</v>
+        <v>404593</v>
       </c>
       <c r="R87" t="n">
-        <v>6758727</v>
+        <v>6758609</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9887,10 +9887,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134065565</v>
+        <v>134065613</v>
       </c>
       <c r="B88" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9898,21 +9898,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9922,10 +9922,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>404911</v>
+        <v>404868</v>
       </c>
       <c r="R88" t="n">
-        <v>6758810</v>
+        <v>6758717</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9994,10 +9994,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134065418</v>
+        <v>134065616</v>
       </c>
       <c r="B89" t="n">
-        <v>79949</v>
+        <v>79366</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10005,21 +10005,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>404822</v>
+        <v>404717</v>
       </c>
       <c r="R89" t="n">
-        <v>6758751</v>
+        <v>6758579</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134065694</v>
+        <v>134065393</v>
       </c>
       <c r="B90" t="n">
-        <v>79025</v>
+        <v>79985</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10112,21 +10112,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>404903</v>
+        <v>404824</v>
       </c>
       <c r="R90" t="n">
-        <v>6758903</v>
+        <v>6758793</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10208,10 +10208,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134065393</v>
+        <v>134065610</v>
       </c>
       <c r="B91" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10219,21 +10219,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>404824</v>
+        <v>404943</v>
       </c>
       <c r="R91" t="n">
-        <v>6758793</v>
+        <v>6758755</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10315,10 +10315,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134065610</v>
+        <v>134065418</v>
       </c>
       <c r="B92" t="n">
-        <v>79359</v>
+        <v>79956</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10326,21 +10326,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>404943</v>
+        <v>404822</v>
       </c>
       <c r="R92" t="n">
-        <v>6758755</v>
+        <v>6758751</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10422,10 +10422,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134065616</v>
+        <v>134065694</v>
       </c>
       <c r="B93" t="n">
-        <v>79359</v>
+        <v>79032</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10433,21 +10433,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>404717</v>
+        <v>404903</v>
       </c>
       <c r="R93" t="n">
-        <v>6758579</v>
+        <v>6758903</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10529,10 +10529,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134065541</v>
+        <v>134065591</v>
       </c>
       <c r="B94" t="n">
-        <v>92013</v>
+        <v>79123</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10540,21 +10540,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10564,10 +10564,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>404532</v>
+        <v>404978</v>
       </c>
       <c r="R94" t="n">
-        <v>6758663</v>
+        <v>6758880</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10639,7 +10639,7 @@
         <v>134065380</v>
       </c>
       <c r="B95" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10743,10 +10743,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134065413</v>
+        <v>134065541</v>
       </c>
       <c r="B96" t="n">
-        <v>79978</v>
+        <v>92020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10754,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10778,10 +10778,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>404527</v>
+        <v>404532</v>
       </c>
       <c r="R96" t="n">
-        <v>6758680</v>
+        <v>6758663</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10850,10 +10850,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134065591</v>
+        <v>134065413</v>
       </c>
       <c r="B97" t="n">
-        <v>79116</v>
+        <v>79985</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10861,21 +10861,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>404978</v>
+        <v>404527</v>
       </c>
       <c r="R97" t="n">
-        <v>6758880</v>
+        <v>6758680</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10957,10 +10957,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134065592</v>
+        <v>134065618</v>
       </c>
       <c r="B98" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10968,21 +10968,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10992,10 +10992,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>404894</v>
+        <v>404705</v>
       </c>
       <c r="R98" t="n">
-        <v>6758696</v>
+        <v>6758564</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11067,7 +11067,7 @@
         <v>134065397</v>
       </c>
       <c r="B99" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11171,10 +11171,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134065398</v>
+        <v>134065394</v>
       </c>
       <c r="B100" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11206,10 +11206,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>404973</v>
+        <v>404814</v>
       </c>
       <c r="R100" t="n">
-        <v>6759009</v>
+        <v>6758813</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11241,7 +11241,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11278,10 +11278,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134065566</v>
+        <v>134065592</v>
       </c>
       <c r="B101" t="n">
-        <v>79117</v>
+        <v>79123</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11289,21 +11289,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>404898</v>
+        <v>404894</v>
       </c>
       <c r="R101" t="n">
-        <v>6758708</v>
+        <v>6758696</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11385,10 +11385,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134065618</v>
+        <v>134065398</v>
       </c>
       <c r="B102" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11396,21 +11396,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11420,10 +11420,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>404705</v>
+        <v>404973</v>
       </c>
       <c r="R102" t="n">
-        <v>6758564</v>
+        <v>6759009</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11492,10 +11492,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134065394</v>
+        <v>134065566</v>
       </c>
       <c r="B103" t="n">
-        <v>79978</v>
+        <v>79124</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11503,21 +11503,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11527,10 +11527,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>404814</v>
+        <v>404898</v>
       </c>
       <c r="R103" t="n">
-        <v>6758813</v>
+        <v>6758708</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11572,7 +11572,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11602,7 +11602,7 @@
         <v>134065379</v>
       </c>
       <c r="B104" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11706,10 +11706,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134065608</v>
+        <v>134065391</v>
       </c>
       <c r="B105" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11717,21 +11717,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11741,10 +11741,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>404872</v>
+        <v>404801</v>
       </c>
       <c r="R105" t="n">
-        <v>6758869</v>
+        <v>6758801</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11816,7 +11816,7 @@
         <v>134065409</v>
       </c>
       <c r="B106" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11920,32 +11920,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134065421</v>
+        <v>134065597</v>
       </c>
       <c r="B107" t="n">
-        <v>79949</v>
+        <v>92146</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11955,10 +11955,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>404659</v>
+        <v>404908</v>
       </c>
       <c r="R107" t="n">
-        <v>6758702</v>
+        <v>6758934</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12027,10 +12027,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134065391</v>
+        <v>134065421</v>
       </c>
       <c r="B108" t="n">
-        <v>79978</v>
+        <v>79956</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12038,21 +12038,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12062,10 +12062,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>404801</v>
+        <v>404659</v>
       </c>
       <c r="R108" t="n">
-        <v>6758801</v>
+        <v>6758702</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12137,7 +12137,7 @@
         <v>134065408</v>
       </c>
       <c r="B109" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12241,32 +12241,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134065597</v>
+        <v>134065608</v>
       </c>
       <c r="B110" t="n">
-        <v>92139</v>
+        <v>79366</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>404908</v>
+        <v>404872</v>
       </c>
       <c r="R110" t="n">
-        <v>6758934</v>
+        <v>6758869</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12351,7 +12351,7 @@
         <v>134065596</v>
       </c>
       <c r="B111" t="n">
-        <v>93269</v>
+        <v>93276</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 20433-2026 artfynd.xlsx
+++ b/artfynd/A 20433-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134065373</v>
+        <v>134065371</v>
       </c>
       <c r="B2" t="n">
-        <v>79398</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>404660</v>
+        <v>404832</v>
       </c>
       <c r="R2" t="n">
-        <v>6758676</v>
+        <v>6758830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134065389</v>
+        <v>134065372</v>
       </c>
       <c r="B3" t="n">
-        <v>79985</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>404773</v>
+        <v>404659</v>
       </c>
       <c r="R3" t="n">
-        <v>6758780</v>
+        <v>6758699</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134065687</v>
+        <v>134065373</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>404824</v>
+        <v>404660</v>
       </c>
       <c r="R4" t="n">
-        <v>6758734</v>
+        <v>6758676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134065415</v>
+        <v>134065374</v>
       </c>
       <c r="B5" t="n">
-        <v>79985</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>404608</v>
+        <v>404663</v>
       </c>
       <c r="R5" t="n">
-        <v>6758706</v>
+        <v>6758651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134065622</v>
+        <v>134065687</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>404532</v>
+        <v>404824</v>
       </c>
       <c r="R6" t="n">
-        <v>6758625</v>
+        <v>6758734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134065612</v>
+        <v>134065688</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>404904</v>
+        <v>404803</v>
       </c>
       <c r="R7" t="n">
-        <v>6758723</v>
+        <v>6758731</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134065606</v>
+        <v>134065689</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>404970</v>
+        <v>404823</v>
       </c>
       <c r="R8" t="n">
-        <v>6758887</v>
+        <v>6758753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134065691</v>
+        <v>134065690</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>404779</v>
+        <v>404796</v>
       </c>
       <c r="R9" t="n">
-        <v>6758789</v>
+        <v>6758771</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134065404</v>
+        <v>134065691</v>
       </c>
       <c r="B10" t="n">
-        <v>79985</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>404881</v>
+        <v>404779</v>
       </c>
       <c r="R10" t="n">
-        <v>6758713</v>
+        <v>6758789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134065697</v>
+        <v>134065692</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>404911</v>
+        <v>404800</v>
       </c>
       <c r="R11" t="n">
-        <v>6758810</v>
+        <v>6758798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134065382</v>
+        <v>134065693</v>
       </c>
       <c r="B12" t="n">
-        <v>79985</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>404824</v>
+        <v>404817</v>
       </c>
       <c r="R12" t="n">
-        <v>6758734</v>
+        <v>6758805</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134065617</v>
+        <v>134065694</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>404715</v>
+        <v>404903</v>
       </c>
       <c r="R13" t="n">
-        <v>6758575</v>
+        <v>6758903</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134065386</v>
+        <v>134065695</v>
       </c>
       <c r="B14" t="n">
-        <v>79985</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>404811</v>
+        <v>404974</v>
       </c>
       <c r="R14" t="n">
-        <v>6758761</v>
+        <v>6758859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134065699</v>
+        <v>134065697</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>404849</v>
+        <v>404911</v>
       </c>
       <c r="R15" t="n">
-        <v>6758743</v>
+        <v>6758810</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134065416</v>
+        <v>134065698</v>
       </c>
       <c r="B16" t="n">
-        <v>79985</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>404659</v>
+        <v>404915</v>
       </c>
       <c r="R16" t="n">
-        <v>6758702</v>
+        <v>6758802</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134065563</v>
+        <v>134065699</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>404771</v>
+        <v>404849</v>
       </c>
       <c r="R17" t="n">
-        <v>6758782</v>
+        <v>6758743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134065706</v>
+        <v>134065700</v>
       </c>
       <c r="B18" t="n">
-        <v>93264</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>404815</v>
+        <v>404740</v>
       </c>
       <c r="R18" t="n">
-        <v>6758798</v>
+        <v>6758628</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134065620</v>
+        <v>134065701</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>404624</v>
+        <v>404593</v>
       </c>
       <c r="R19" t="n">
-        <v>6758605</v>
+        <v>6758609</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134065387</v>
+        <v>134065703</v>
       </c>
       <c r="B20" t="n">
-        <v>79985</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>404796</v>
+        <v>404667</v>
       </c>
       <c r="R20" t="n">
-        <v>6758769</v>
+        <v>6758545</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,32 +2708,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134065603</v>
+        <v>134065597</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>92153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>404788</v>
+        <v>404908</v>
       </c>
       <c r="R21" t="n">
-        <v>6758782</v>
+        <v>6758934</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134065567</v>
+        <v>134065541</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>92027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,21 +2826,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>404673</v>
+        <v>404532</v>
       </c>
       <c r="R22" t="n">
-        <v>6758546</v>
+        <v>6758663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134065537</v>
+        <v>134065534</v>
       </c>
       <c r="B23" t="n">
-        <v>79390</v>
+        <v>93263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6434</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>404567</v>
+        <v>404836</v>
       </c>
       <c r="R23" t="n">
-        <v>6758595</v>
+        <v>6758673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3002,14 +3002,19 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -3029,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134065722</v>
+        <v>134065705</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>93271</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3040,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>404791</v>
+        <v>404776</v>
       </c>
       <c r="R24" t="n">
-        <v>6758773</v>
+        <v>6758787</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3109,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134065390</v>
+        <v>134065706</v>
       </c>
       <c r="B25" t="n">
-        <v>79985</v>
+        <v>93271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3152,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>404779</v>
+        <v>404815</v>
       </c>
       <c r="R25" t="n">
-        <v>6758789</v>
+        <v>6758798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3216,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134065407</v>
+        <v>134065708</v>
       </c>
       <c r="B26" t="n">
-        <v>79985</v>
+        <v>93271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,21 +3259,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>404727</v>
+        <v>404938</v>
       </c>
       <c r="R26" t="n">
-        <v>6758620</v>
+        <v>6758745</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,7 +3318,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3323,7 +3328,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3355,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134065381</v>
+        <v>134065596</v>
       </c>
       <c r="B27" t="n">
-        <v>79985</v>
+        <v>93283</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3361,34 +3366,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>404845</v>
+        <v>404834</v>
       </c>
       <c r="R27" t="n">
-        <v>6758668</v>
+        <v>6758675</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3428,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3430,7 +3438,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,6 +3446,11 @@
       </c>
       <c r="AE27" t="b">
         <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -3457,32 +3470,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134065703</v>
+        <v>134065603</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3492,10 +3505,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>404667</v>
+        <v>404788</v>
       </c>
       <c r="R28" t="n">
-        <v>6758545</v>
+        <v>6758782</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3540,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3537,7 +3550,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3564,32 +3577,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134065723</v>
+        <v>134065604</v>
       </c>
       <c r="B29" t="n">
-        <v>78769</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3599,10 +3612,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>404582</v>
+        <v>404978</v>
       </c>
       <c r="R29" t="n">
-        <v>6758712</v>
+        <v>6758991</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3647,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3644,7 +3657,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3671,32 +3684,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134065412</v>
+        <v>134065605</v>
       </c>
       <c r="B30" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3719,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>404548</v>
+        <v>404960</v>
       </c>
       <c r="R30" t="n">
-        <v>6758612</v>
+        <v>6758909</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3741,7 +3754,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3751,7 +3764,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3778,32 +3791,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134065401</v>
+        <v>134065606</v>
       </c>
       <c r="B31" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3813,10 +3826,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>404911</v>
+        <v>404970</v>
       </c>
       <c r="R31" t="n">
-        <v>6758810</v>
+        <v>6758887</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,7 +3861,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3858,7 +3871,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3885,32 +3898,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134065371</v>
+        <v>134065607</v>
       </c>
       <c r="B32" t="n">
-        <v>79398</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3933,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>404832</v>
+        <v>404936</v>
       </c>
       <c r="R32" t="n">
-        <v>6758830</v>
+        <v>6758864</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3955,7 +3968,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3965,7 +3978,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,14 +4005,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134065609</v>
+        <v>134065608</v>
       </c>
       <c r="B33" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4027,10 +4040,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>404917</v>
+        <v>404872</v>
       </c>
       <c r="R33" t="n">
-        <v>6758763</v>
+        <v>6758869</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4062,7 +4075,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4072,7 +4085,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,14 +4112,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134065626</v>
+        <v>134065609</v>
       </c>
       <c r="B34" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4134,10 +4147,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>404666</v>
+        <v>404917</v>
       </c>
       <c r="R34" t="n">
-        <v>6758664</v>
+        <v>6758763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4169,7 +4182,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4179,7 +4192,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4206,32 +4219,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134065410</v>
+        <v>134065610</v>
       </c>
       <c r="B35" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4241,10 +4254,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>404594</v>
+        <v>404943</v>
       </c>
       <c r="R35" t="n">
-        <v>6758606</v>
+        <v>6758755</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4276,7 +4289,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4286,7 +4299,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4313,32 +4326,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134065708</v>
+        <v>134065611</v>
       </c>
       <c r="B36" t="n">
-        <v>93264</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4351,7 +4364,7 @@
         <v>404938</v>
       </c>
       <c r="R36" t="n">
-        <v>6758745</v>
+        <v>6758735</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,7 +4396,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4393,7 +4406,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,32 +4433,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134065692</v>
+        <v>134065612</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4455,10 +4468,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404800</v>
+        <v>404904</v>
       </c>
       <c r="R37" t="n">
-        <v>6758798</v>
+        <v>6758723</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4490,7 +4503,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4500,7 +4513,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4527,14 +4540,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134065611</v>
+        <v>134065613</v>
       </c>
       <c r="B38" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4562,10 +4575,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404938</v>
+        <v>404868</v>
       </c>
       <c r="R38" t="n">
-        <v>6758735</v>
+        <v>6758717</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4610,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4607,7 +4620,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4634,32 +4647,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134065405</v>
+        <v>134065614</v>
       </c>
       <c r="B39" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4669,10 +4682,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404840</v>
+        <v>404734</v>
       </c>
       <c r="R39" t="n">
-        <v>6758734</v>
+        <v>6758630</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4704,7 +4717,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4714,7 +4727,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,32 +4754,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134065399</v>
+        <v>134065615</v>
       </c>
       <c r="B40" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4776,10 +4789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404968</v>
+        <v>404723</v>
       </c>
       <c r="R40" t="n">
-        <v>6758922</v>
+        <v>6758594</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4811,7 +4824,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4821,7 +4834,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4848,32 +4861,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134065690</v>
+        <v>134065616</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4883,10 +4896,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404796</v>
+        <v>404717</v>
       </c>
       <c r="R41" t="n">
-        <v>6758771</v>
+        <v>6758579</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,7 +4931,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4928,7 +4941,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4955,32 +4968,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134065693</v>
+        <v>134065617</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4990,10 +5003,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404817</v>
+        <v>404715</v>
       </c>
       <c r="R42" t="n">
-        <v>6758805</v>
+        <v>6758575</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5025,7 +5038,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5035,7 +5048,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5062,32 +5075,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134065698</v>
+        <v>134065618</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5097,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404915</v>
+        <v>404705</v>
       </c>
       <c r="R43" t="n">
-        <v>6758802</v>
+        <v>6758564</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5132,7 +5145,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5142,7 +5155,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5169,32 +5182,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134065403</v>
+        <v>134065619</v>
       </c>
       <c r="B44" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5217,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404906</v>
+        <v>404697</v>
       </c>
       <c r="R44" t="n">
-        <v>6758705</v>
+        <v>6758567</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5239,7 +5252,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5249,7 +5262,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5276,32 +5289,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134065564</v>
+        <v>134065620</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5311,10 +5324,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404972</v>
+        <v>404624</v>
       </c>
       <c r="R45" t="n">
-        <v>6758882</v>
+        <v>6758605</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5346,7 +5359,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5356,7 +5369,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,32 +5396,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134065689</v>
+        <v>134065621</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5418,10 +5431,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404823</v>
+        <v>404593</v>
       </c>
       <c r="R46" t="n">
-        <v>6758753</v>
+        <v>6758609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5453,7 +5466,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5463,7 +5476,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,32 +5503,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134065384</v>
+        <v>134065622</v>
       </c>
       <c r="B47" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5525,10 +5538,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404810</v>
+        <v>404532</v>
       </c>
       <c r="R47" t="n">
-        <v>6758738</v>
+        <v>6758625</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5560,7 +5573,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5570,7 +5583,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5597,32 +5610,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134065388</v>
+        <v>134065623</v>
       </c>
       <c r="B48" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5632,10 +5645,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404787</v>
+        <v>404582</v>
       </c>
       <c r="R48" t="n">
-        <v>6758776</v>
+        <v>6758712</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,7 +5680,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5677,7 +5690,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5704,32 +5717,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134065372</v>
+        <v>134065624</v>
       </c>
       <c r="B49" t="n">
-        <v>79398</v>
+        <v>79373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5739,10 +5752,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404659</v>
+        <v>404660</v>
       </c>
       <c r="R49" t="n">
-        <v>6758699</v>
+        <v>6758694</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5811,32 +5824,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134065535</v>
+        <v>134065625</v>
       </c>
       <c r="B50" t="n">
-        <v>79390</v>
+        <v>79373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5846,10 +5859,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404829</v>
+        <v>404658</v>
       </c>
       <c r="R50" t="n">
-        <v>6758826</v>
+        <v>6758686</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,7 +5894,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5891,7 +5904,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5918,32 +5931,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134065561</v>
+        <v>134065626</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5953,10 +5966,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404847</v>
+        <v>404666</v>
       </c>
       <c r="R51" t="n">
-        <v>6758670</v>
+        <v>6758664</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,7 +6001,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5998,7 +6011,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6025,32 +6038,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134065395</v>
+        <v>134065627</v>
       </c>
       <c r="B52" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6060,10 +6073,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404888</v>
+        <v>404660</v>
       </c>
       <c r="R52" t="n">
-        <v>6758894</v>
+        <v>6758643</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6095,7 +6108,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6105,7 +6118,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6132,14 +6145,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134065624</v>
+        <v>134065629</v>
       </c>
       <c r="B53" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6167,10 +6180,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404660</v>
+        <v>404677</v>
       </c>
       <c r="R53" t="n">
-        <v>6758694</v>
+        <v>6758528</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6202,7 +6215,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6212,7 +6225,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6239,50 +6252,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134065496</v>
+        <v>134065535</v>
       </c>
       <c r="B54" t="n">
-        <v>57972</v>
+        <v>79397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404969</v>
+        <v>404829</v>
       </c>
       <c r="R54" t="n">
-        <v>6758939</v>
+        <v>6758826</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6314,7 +6322,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6324,7 +6332,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6351,32 +6359,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134065721</v>
+        <v>134065536</v>
       </c>
       <c r="B55" t="n">
-        <v>78370</v>
+        <v>79397</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6487</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6386,10 +6394,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404791</v>
+        <v>404959</v>
       </c>
       <c r="R55" t="n">
-        <v>6758773</v>
+        <v>6758961</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6421,7 +6429,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6431,7 +6439,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6458,32 +6466,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134065419</v>
+        <v>134065537</v>
       </c>
       <c r="B56" t="n">
-        <v>79956</v>
+        <v>79397</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6493,10 +6501,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404782</v>
+        <v>404567</v>
       </c>
       <c r="R56" t="n">
-        <v>6758790</v>
+        <v>6758595</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6528,7 +6536,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6538,7 +6546,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6565,32 +6573,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134065385</v>
+        <v>134065538</v>
       </c>
       <c r="B57" t="n">
-        <v>79985</v>
+        <v>79397</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6600,10 +6608,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404814</v>
+        <v>404572</v>
       </c>
       <c r="R57" t="n">
-        <v>6758745</v>
+        <v>6758703</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6635,7 +6643,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6645,7 +6653,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6672,32 +6680,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134065705</v>
+        <v>134065722</v>
       </c>
       <c r="B58" t="n">
-        <v>93264</v>
+        <v>78776</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6707,10 +6715,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404776</v>
+        <v>404791</v>
       </c>
       <c r="R58" t="n">
-        <v>6758787</v>
+        <v>6758773</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6742,7 +6750,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6752,7 +6760,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6779,10 +6787,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134065629</v>
+        <v>134065723</v>
       </c>
       <c r="B59" t="n">
-        <v>79366</v>
+        <v>78776</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6790,21 +6798,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6814,10 +6822,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404677</v>
+        <v>404582</v>
       </c>
       <c r="R59" t="n">
-        <v>6758528</v>
+        <v>6758712</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6849,7 +6857,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6859,7 +6867,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6886,32 +6894,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134065538</v>
+        <v>134065591</v>
       </c>
       <c r="B60" t="n">
-        <v>79390</v>
+        <v>79130</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6921,10 +6929,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404572</v>
+        <v>404978</v>
       </c>
       <c r="R60" t="n">
-        <v>6758703</v>
+        <v>6758880</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6956,7 +6964,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6966,7 +6974,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6993,10 +7001,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134065604</v>
+        <v>134065592</v>
       </c>
       <c r="B61" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7004,21 +7012,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7028,10 +7036,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404978</v>
+        <v>404894</v>
       </c>
       <c r="R61" t="n">
-        <v>6758991</v>
+        <v>6758696</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7063,7 +7071,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7073,7 +7081,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7100,10 +7108,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134065701</v>
+        <v>134065593</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>79130</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7111,21 +7119,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7135,10 +7143,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404593</v>
+        <v>404673</v>
       </c>
       <c r="R62" t="n">
-        <v>6758609</v>
+        <v>6758546</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7170,7 +7178,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7180,7 +7188,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7207,10 +7215,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134065623</v>
+        <v>134065379</v>
       </c>
       <c r="B63" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7218,21 +7226,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7242,10 +7250,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404582</v>
+        <v>404856</v>
       </c>
       <c r="R63" t="n">
-        <v>6758712</v>
+        <v>6758644</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7277,7 +7285,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7287,7 +7295,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7314,10 +7322,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134065607</v>
+        <v>134065380</v>
       </c>
       <c r="B64" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,21 +7333,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7349,10 +7357,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404936</v>
+        <v>404851</v>
       </c>
       <c r="R64" t="n">
-        <v>6758864</v>
+        <v>6758657</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7384,7 +7392,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7394,7 +7402,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7421,10 +7429,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134065605</v>
+        <v>134065381</v>
       </c>
       <c r="B65" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7432,21 +7440,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7456,10 +7464,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404960</v>
+        <v>404845</v>
       </c>
       <c r="R65" t="n">
-        <v>6758909</v>
+        <v>6758668</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7491,7 +7499,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7501,7 +7509,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7528,10 +7536,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134065619</v>
+        <v>134065382</v>
       </c>
       <c r="B66" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7539,21 +7547,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7563,10 +7571,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404697</v>
+        <v>404824</v>
       </c>
       <c r="R66" t="n">
-        <v>6758567</v>
+        <v>6758734</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7598,7 +7606,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7608,7 +7616,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7635,10 +7643,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134065402</v>
+        <v>134065383</v>
       </c>
       <c r="B67" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7670,10 +7678,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404938</v>
+        <v>404810</v>
       </c>
       <c r="R67" t="n">
-        <v>6758742</v>
+        <v>6758727</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7705,7 +7713,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7715,7 +7723,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7742,10 +7750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134065396</v>
+        <v>134065384</v>
       </c>
       <c r="B68" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7777,10 +7785,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404893</v>
+        <v>404810</v>
       </c>
       <c r="R68" t="n">
-        <v>6758895</v>
+        <v>6758738</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7812,7 +7820,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7822,7 +7830,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7849,10 +7857,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134065411</v>
+        <v>134065385</v>
       </c>
       <c r="B69" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7884,10 +7892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404590</v>
+        <v>404814</v>
       </c>
       <c r="R69" t="n">
-        <v>6758604</v>
+        <v>6758745</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7919,7 +7927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7929,7 +7937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7956,10 +7964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134065695</v>
+        <v>134065386</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79992</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7967,21 +7975,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7991,10 +7999,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404974</v>
+        <v>404811</v>
       </c>
       <c r="R70" t="n">
-        <v>6758859</v>
+        <v>6758761</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8026,7 +8034,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8036,7 +8044,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8063,10 +8071,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134065417</v>
+        <v>134065387</v>
       </c>
       <c r="B71" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8098,10 +8106,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404662</v>
+        <v>404796</v>
       </c>
       <c r="R71" t="n">
-        <v>6758649</v>
+        <v>6758769</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8133,7 +8141,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8143,7 +8151,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8170,10 +8178,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134065627</v>
+        <v>134065388</v>
       </c>
       <c r="B72" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8181,21 +8189,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8205,10 +8213,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404660</v>
+        <v>404787</v>
       </c>
       <c r="R72" t="n">
-        <v>6758643</v>
+        <v>6758776</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8240,7 +8248,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8250,7 +8258,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8277,10 +8285,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134065374</v>
+        <v>134065389</v>
       </c>
       <c r="B73" t="n">
-        <v>79398</v>
+        <v>79992</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8288,21 +8296,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8312,10 +8320,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404663</v>
+        <v>404773</v>
       </c>
       <c r="R73" t="n">
-        <v>6758651</v>
+        <v>6758780</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8347,7 +8355,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8357,7 +8365,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8384,10 +8392,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134065615</v>
+        <v>134065390</v>
       </c>
       <c r="B74" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8395,21 +8403,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8419,10 +8427,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404723</v>
+        <v>404779</v>
       </c>
       <c r="R74" t="n">
-        <v>6758594</v>
+        <v>6758789</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8454,7 +8462,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8464,7 +8472,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8491,10 +8499,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134065400</v>
+        <v>134065391</v>
       </c>
       <c r="B75" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8526,10 +8534,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404899</v>
+        <v>404801</v>
       </c>
       <c r="R75" t="n">
-        <v>6758863</v>
+        <v>6758801</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8561,7 +8569,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8571,7 +8579,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8598,10 +8606,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134065562</v>
+        <v>134065392</v>
       </c>
       <c r="B76" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8609,21 +8617,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8633,10 +8641,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404815</v>
+        <v>404778</v>
       </c>
       <c r="R76" t="n">
-        <v>6758748</v>
+        <v>6758818</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8668,7 +8676,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8678,7 +8686,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8705,10 +8713,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134065614</v>
+        <v>134065393</v>
       </c>
       <c r="B77" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8716,21 +8724,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8740,10 +8748,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404734</v>
+        <v>404824</v>
       </c>
       <c r="R77" t="n">
-        <v>6758630</v>
+        <v>6758793</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8775,7 +8783,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8785,7 +8793,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,10 +8820,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134065534</v>
+        <v>134065394</v>
       </c>
       <c r="B78" t="n">
-        <v>93256</v>
+        <v>79992</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8823,21 +8831,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8847,10 +8855,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404836</v>
+        <v>404814</v>
       </c>
       <c r="R78" t="n">
-        <v>6758673</v>
+        <v>6758813</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8882,7 +8890,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8892,19 +8900,14 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:39</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -8924,10 +8927,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134065688</v>
+        <v>134065395</v>
       </c>
       <c r="B79" t="n">
-        <v>79032</v>
+        <v>79992</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8935,21 +8938,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8959,10 +8962,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404803</v>
+        <v>404888</v>
       </c>
       <c r="R79" t="n">
-        <v>6758731</v>
+        <v>6758894</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8994,7 +8997,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9004,7 +9007,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9031,10 +9034,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134065593</v>
+        <v>134065396</v>
       </c>
       <c r="B80" t="n">
-        <v>79123</v>
+        <v>79992</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9042,21 +9045,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9066,10 +9069,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>404673</v>
+        <v>404893</v>
       </c>
       <c r="R80" t="n">
-        <v>6758546</v>
+        <v>6758895</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9101,7 +9104,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9111,7 +9114,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9138,10 +9141,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134065625</v>
+        <v>134065397</v>
       </c>
       <c r="B81" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9149,21 +9152,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9173,10 +9176,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>404658</v>
+        <v>404910</v>
       </c>
       <c r="R81" t="n">
-        <v>6758686</v>
+        <v>6758935</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9208,7 +9211,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9218,7 +9221,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9245,10 +9248,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134065392</v>
+        <v>134065398</v>
       </c>
       <c r="B82" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9280,10 +9283,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>404778</v>
+        <v>404973</v>
       </c>
       <c r="R82" t="n">
-        <v>6758818</v>
+        <v>6759009</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9315,7 +9318,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9325,7 +9328,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9352,10 +9355,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134065406</v>
+        <v>134065399</v>
       </c>
       <c r="B83" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9387,10 +9390,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>404736</v>
+        <v>404968</v>
       </c>
       <c r="R83" t="n">
-        <v>6758627</v>
+        <v>6758922</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9422,7 +9425,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9432,7 +9435,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9459,10 +9462,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134065383</v>
+        <v>134065400</v>
       </c>
       <c r="B84" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9494,10 +9497,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>404810</v>
+        <v>404899</v>
       </c>
       <c r="R84" t="n">
-        <v>6758727</v>
+        <v>6758863</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9529,7 +9532,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9539,7 +9542,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9566,10 +9569,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134065565</v>
+        <v>134065401</v>
       </c>
       <c r="B85" t="n">
-        <v>79124</v>
+        <v>79992</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9577,21 +9580,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9673,32 +9676,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134065536</v>
+        <v>134065402</v>
       </c>
       <c r="B86" t="n">
-        <v>79390</v>
+        <v>79992</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9708,10 +9711,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>404959</v>
+        <v>404938</v>
       </c>
       <c r="R86" t="n">
-        <v>6758961</v>
+        <v>6758742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9743,7 +9746,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9753,7 +9756,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9780,10 +9783,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134065621</v>
+        <v>134065403</v>
       </c>
       <c r="B87" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9791,21 +9794,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9815,10 +9818,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>404593</v>
+        <v>404906</v>
       </c>
       <c r="R87" t="n">
-        <v>6758609</v>
+        <v>6758705</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9850,7 +9853,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9860,7 +9863,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9887,10 +9890,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134065613</v>
+        <v>134065404</v>
       </c>
       <c r="B88" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9898,21 +9901,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9922,10 +9925,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>404868</v>
+        <v>404881</v>
       </c>
       <c r="R88" t="n">
-        <v>6758717</v>
+        <v>6758713</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9994,10 +9997,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134065616</v>
+        <v>134065405</v>
       </c>
       <c r="B89" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10005,21 +10008,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10029,10 +10032,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>404717</v>
+        <v>404840</v>
       </c>
       <c r="R89" t="n">
-        <v>6758579</v>
+        <v>6758734</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10064,7 +10067,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10074,7 +10077,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10101,10 +10104,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134065393</v>
+        <v>134065406</v>
       </c>
       <c r="B90" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10136,10 +10139,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>404824</v>
+        <v>404736</v>
       </c>
       <c r="R90" t="n">
-        <v>6758793</v>
+        <v>6758627</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,7 +10174,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10181,7 +10184,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10208,10 +10211,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134065610</v>
+        <v>134065407</v>
       </c>
       <c r="B91" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10219,21 +10222,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10243,10 +10246,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>404943</v>
+        <v>404727</v>
       </c>
       <c r="R91" t="n">
-        <v>6758755</v>
+        <v>6758620</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10278,7 +10281,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10288,7 +10291,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10315,10 +10318,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134065418</v>
+        <v>134065408</v>
       </c>
       <c r="B92" t="n">
-        <v>79956</v>
+        <v>79992</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10326,21 +10329,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10350,10 +10353,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>404822</v>
+        <v>404632</v>
       </c>
       <c r="R92" t="n">
-        <v>6758751</v>
+        <v>6758586</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10385,7 +10388,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10395,7 +10398,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10422,10 +10425,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134065694</v>
+        <v>134065409</v>
       </c>
       <c r="B93" t="n">
-        <v>79032</v>
+        <v>79992</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10433,21 +10436,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10457,10 +10460,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>404903</v>
+        <v>404630</v>
       </c>
       <c r="R93" t="n">
-        <v>6758903</v>
+        <v>6758588</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10492,7 +10495,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10502,7 +10505,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10529,10 +10532,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134065591</v>
+        <v>134065410</v>
       </c>
       <c r="B94" t="n">
-        <v>79123</v>
+        <v>79992</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10540,21 +10543,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10564,10 +10567,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>404978</v>
+        <v>404594</v>
       </c>
       <c r="R94" t="n">
-        <v>6758880</v>
+        <v>6758606</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10599,7 +10602,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10609,7 +10612,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10636,10 +10639,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134065380</v>
+        <v>134065411</v>
       </c>
       <c r="B95" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10671,10 +10674,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>404851</v>
+        <v>404590</v>
       </c>
       <c r="R95" t="n">
-        <v>6758657</v>
+        <v>6758604</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10706,7 +10709,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10716,7 +10719,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,10 +10746,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134065541</v>
+        <v>134065412</v>
       </c>
       <c r="B96" t="n">
-        <v>92020</v>
+        <v>79992</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10754,21 +10757,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10778,10 +10781,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>404532</v>
+        <v>404548</v>
       </c>
       <c r="R96" t="n">
-        <v>6758663</v>
+        <v>6758612</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10813,7 +10816,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10823,7 +10826,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10853,7 +10856,7 @@
         <v>134065413</v>
       </c>
       <c r="B97" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10957,10 +10960,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134065618</v>
+        <v>134065415</v>
       </c>
       <c r="B98" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10968,21 +10971,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10992,10 +10995,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>404705</v>
+        <v>404608</v>
       </c>
       <c r="R98" t="n">
-        <v>6758564</v>
+        <v>6758706</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11027,7 +11030,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11037,7 +11040,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11064,10 +11067,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134065397</v>
+        <v>134065416</v>
       </c>
       <c r="B99" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11099,10 +11102,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>404910</v>
+        <v>404659</v>
       </c>
       <c r="R99" t="n">
-        <v>6758935</v>
+        <v>6758702</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11134,7 +11137,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11144,7 +11147,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11171,10 +11174,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134065394</v>
+        <v>134065417</v>
       </c>
       <c r="B100" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11206,10 +11209,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>404814</v>
+        <v>404662</v>
       </c>
       <c r="R100" t="n">
-        <v>6758813</v>
+        <v>6758649</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11241,7 +11244,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11251,7 +11254,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11278,10 +11281,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134065592</v>
+        <v>134065721</v>
       </c>
       <c r="B101" t="n">
-        <v>79123</v>
+        <v>78377</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11289,21 +11292,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11313,10 +11316,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>404894</v>
+        <v>404791</v>
       </c>
       <c r="R101" t="n">
-        <v>6758696</v>
+        <v>6758773</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11348,7 +11351,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11358,7 +11361,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11385,45 +11388,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134065398</v>
+        <v>134065496</v>
       </c>
       <c r="B102" t="n">
-        <v>79985</v>
+        <v>57972</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>404973</v>
+        <v>404969</v>
       </c>
       <c r="R102" t="n">
-        <v>6759009</v>
+        <v>6758939</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11455,7 +11463,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11465,7 +11473,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11492,32 +11500,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134065566</v>
+        <v>134065679</v>
       </c>
       <c r="B103" t="n">
-        <v>79124</v>
+        <v>79057</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>228659</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fönsterlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia stellaris</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11527,10 +11535,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>404898</v>
+        <v>404903</v>
       </c>
       <c r="R103" t="n">
-        <v>6758708</v>
+        <v>6758903</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11562,7 +11570,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11572,7 +11580,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11599,10 +11607,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134065379</v>
+        <v>134065561</v>
       </c>
       <c r="B104" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11610,21 +11618,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11634,10 +11642,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>404856</v>
+        <v>404847</v>
       </c>
       <c r="R104" t="n">
-        <v>6758644</v>
+        <v>6758670</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11669,7 +11677,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11679,7 +11687,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11706,10 +11714,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134065391</v>
+        <v>134065562</v>
       </c>
       <c r="B105" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11717,21 +11725,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11741,10 +11749,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>404801</v>
+        <v>404815</v>
       </c>
       <c r="R105" t="n">
-        <v>6758801</v>
+        <v>6758748</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11776,7 +11784,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11786,7 +11794,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11813,10 +11821,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134065409</v>
+        <v>134065563</v>
       </c>
       <c r="B106" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11824,21 +11832,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11848,10 +11856,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>404630</v>
+        <v>404771</v>
       </c>
       <c r="R106" t="n">
-        <v>6758588</v>
+        <v>6758782</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11883,7 +11891,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11893,7 +11901,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11920,32 +11928,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134065597</v>
+        <v>134065564</v>
       </c>
       <c r="B107" t="n">
-        <v>92146</v>
+        <v>79131</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11955,10 +11963,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>404908</v>
+        <v>404972</v>
       </c>
       <c r="R107" t="n">
-        <v>6758934</v>
+        <v>6758882</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11990,7 +11998,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12000,7 +12008,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12027,10 +12035,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134065421</v>
+        <v>134065565</v>
       </c>
       <c r="B108" t="n">
-        <v>79956</v>
+        <v>79131</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12038,21 +12046,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12062,10 +12070,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>404659</v>
+        <v>404911</v>
       </c>
       <c r="R108" t="n">
-        <v>6758702</v>
+        <v>6758810</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12097,7 +12105,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12107,7 +12115,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12134,10 +12142,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134065408</v>
+        <v>134065566</v>
       </c>
       <c r="B109" t="n">
-        <v>79985</v>
+        <v>79131</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12145,21 +12153,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12169,10 +12177,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>404632</v>
+        <v>404898</v>
       </c>
       <c r="R109" t="n">
-        <v>6758586</v>
+        <v>6758708</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12204,7 +12212,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12214,7 +12222,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12241,10 +12249,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134065608</v>
+        <v>134065567</v>
       </c>
       <c r="B110" t="n">
-        <v>79366</v>
+        <v>79131</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12252,21 +12260,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12276,10 +12284,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>404872</v>
+        <v>404673</v>
       </c>
       <c r="R110" t="n">
-        <v>6758869</v>
+        <v>6758546</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12311,7 +12319,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12321,7 +12329,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12348,48 +12356,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134065596</v>
+        <v>134065418</v>
       </c>
       <c r="B111" t="n">
-        <v>93276</v>
+        <v>79963</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4366</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Strandkölen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>404834</v>
+        <v>404822</v>
       </c>
       <c r="R111" t="n">
-        <v>6758675</v>
+        <v>6758751</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12421,7 +12426,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12431,7 +12436,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12439,11 +12444,6 @@
       </c>
       <c r="AE111" t="b">
         <v>0</v>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
@@ -12460,6 +12460,220 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>134065419</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Strandkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>404782</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6758790</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>134065421</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Strandkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>404659</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6758702</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20433-2026 artfynd.xlsx
+++ b/artfynd/A 20433-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AZ113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065372</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065374</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065687</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065688</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065689</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065690</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065691</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065692</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065693</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065694</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065695</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065697</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065698</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065699</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065700</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065701</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065597</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065541</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3031,6 +3141,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065534</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3138,6 +3253,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065705</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3245,6 +3365,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065706</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3352,6 +3477,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065708</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3467,6 +3597,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065596</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3574,6 +3709,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065603</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3681,6 +3821,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065604</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3788,6 +3933,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065605</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3895,6 +4045,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065606</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4002,6 +4157,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065607</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4109,6 +4269,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065608</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4216,6 +4381,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065609</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4323,6 +4493,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065610</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4430,6 +4605,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065611</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4537,6 +4717,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065612</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4644,6 +4829,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065613</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4751,6 +4941,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065614</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4858,6 +5053,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065615</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4965,6 +5165,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065616</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5072,6 +5277,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065617</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5179,6 +5389,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065618</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5286,6 +5501,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065619</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5393,6 +5613,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065620</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5500,6 +5725,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065621</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5607,6 +5837,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065622</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5714,6 +5949,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065623</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5821,6 +6061,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065624</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5928,6 +6173,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065625</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6035,6 +6285,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065626</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6142,6 +6397,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065627</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6249,6 +6509,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065629</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6356,6 +6621,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065535</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6463,6 +6733,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065536</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6570,6 +6845,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065537</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6677,6 +6957,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065538</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6784,6 +7069,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065722</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6891,6 +7181,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065723</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6998,6 +7293,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065591</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7105,6 +7405,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065592</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7212,6 +7517,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065593</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7319,6 +7629,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065379</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7426,6 +7741,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065380</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7533,6 +7853,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065381</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7640,6 +7965,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065382</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7747,6 +8077,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065383</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7854,6 +8189,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065384</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7961,6 +8301,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065385</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8068,6 +8413,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065386</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8175,6 +8525,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065387</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8282,6 +8637,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065388</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8389,6 +8749,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065389</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8496,6 +8861,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065390</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8603,6 +8973,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065391</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8710,6 +9085,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065392</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8817,6 +9197,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065393</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8924,6 +9309,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065394</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9031,6 +9421,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065395</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9138,6 +9533,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065396</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9245,6 +9645,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065397</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9352,6 +9757,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065398</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9459,6 +9869,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065399</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9566,6 +9981,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065400</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9673,6 +10093,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065401</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9780,6 +10205,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065402</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9887,6 +10317,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065403</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9994,6 +10429,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065404</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10101,6 +10541,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065405</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10208,6 +10653,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065406</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10315,6 +10765,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065407</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10422,6 +10877,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065408</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10529,6 +10989,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065409</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10636,6 +11101,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065410</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10743,6 +11213,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065411</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10850,6 +11325,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065412</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10957,6 +11437,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065413</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11064,6 +11549,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065415</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11171,6 +11661,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065416</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11278,6 +11773,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065417</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11385,6 +11885,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065721</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11497,6 +12002,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065496</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11604,6 +12114,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065679</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11711,6 +12226,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065561</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11818,6 +12338,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065562</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11925,6 +12450,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065563</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12032,6 +12562,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065564</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12139,6 +12674,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065565</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12246,6 +12786,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065566</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12353,6 +12898,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065567</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12460,6 +13010,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065418</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12567,6 +13122,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065419</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12674,8 +13234,127 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134065421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>